--- a/evaluation/data/parents_responses.xlsx
+++ b/evaluation/data/parents_responses.xlsx
@@ -455,7 +455,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Do you consider the activity log of your children useful?</t>
+          <t>Do you consider it useful to view the activity log of your children?</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
